--- a/data/gravel/Sour Pasta Party 2025.xlsx
+++ b/data/gravel/Sour Pasta Party 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93B23054-5A34-3647-9F4F-6AE84D055B93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{378D252B-C9D9-E54E-9ABF-BBF850B34135}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="10000" yWindow="860" windowWidth="18800" windowHeight="16760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="108">
   <si>
     <t>brand</t>
   </si>
@@ -354,6 +354,9 @@
   </si>
   <si>
     <t>1099 frame</t>
+  </si>
+  <si>
+    <t>https://sour.bike/wp-content/uploads/2024/10/B0A5674-Pano-Edit-2048x1280.jpg</t>
   </si>
 </sst>
 </file>
@@ -739,6 +742,11 @@
         <v>98</v>
       </c>
     </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>107</v>
+      </c>
+    </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>

--- a/data/gravel/Sour Pasta Party 2025.xlsx
+++ b/data/gravel/Sour Pasta Party 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{378D252B-C9D9-E54E-9ABF-BBF850B34135}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77D06720-702C-E441-8790-683FE6732D36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="10000" yWindow="860" windowWidth="18800" windowHeight="16760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="110">
   <si>
     <t>brand</t>
   </si>
@@ -357,6 +357,12 @@
   </si>
   <si>
     <t>https://sour.bike/wp-content/uploads/2024/10/B0A5674-Pano-Edit-2048x1280.jpg</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Dresden, Germany</t>
   </si>
 </sst>
 </file>
@@ -696,7 +702,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F72"/>
+  <dimension ref="A1:F73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1457,6 +1463,14 @@
         <v>104</v>
       </c>
     </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>108</v>
+      </c>
+      <c r="B73" t="s">
+        <v>109</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Sour Pasta Party 2025.xlsx
+++ b/data/gravel/Sour Pasta Party 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77D06720-702C-E441-8790-683FE6732D36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{806B0329-4062-9B40-99B9-48B9FC7F26C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="10000" yWindow="860" windowWidth="18800" windowHeight="16760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="116">
   <si>
     <t>brand</t>
   </si>
@@ -363,6 +363,24 @@
   </si>
   <si>
     <t>Dresden, Germany</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -702,7 +720,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F73"/>
+  <dimension ref="A1:F79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1296,178 +1314,208 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>45</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>46</v>
+        <v>111</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>47</v>
-      </c>
-      <c r="B51">
-        <v>31.6</v>
+        <v>112</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>48</v>
-      </c>
-      <c r="B52" s="2"/>
+        <v>113</v>
+      </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>49</v>
-      </c>
-      <c r="B53">
-        <v>38</v>
+        <v>114</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>50</v>
+        <v>115</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>51</v>
+        <v>45</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>52</v>
-      </c>
-      <c r="B56">
-        <v>160</v>
+        <v>46</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>53</v>
+        <v>47</v>
+      </c>
+      <c r="B57">
+        <v>31.6</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>54</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>75</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="B58" s="2"/>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>55</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>76</v>
+        <v>49</v>
+      </c>
+      <c r="B59">
+        <v>38</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>56</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>72</v>
+        <v>50</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B62">
-        <v>2</v>
+        <v>160</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>59</v>
-      </c>
-      <c r="B63">
-        <v>1</v>
+        <v>53</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>103</v>
+        <v>75</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>61</v>
-      </c>
-      <c r="B65">
-        <v>3</v>
+        <v>55</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>62</v>
-      </c>
-      <c r="B66" s="2"/>
+        <v>56</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>63</v>
-      </c>
-      <c r="B67" s="2"/>
+        <v>57</v>
+      </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>64</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>103</v>
+        <v>58</v>
+      </c>
+      <c r="B68">
+        <v>2</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
+        <v>59</v>
+      </c>
+      <c r="B69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>60</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>61</v>
+      </c>
+      <c r="B71">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>62</v>
+      </c>
+      <c r="B72" s="2"/>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>63</v>
+      </c>
+      <c r="B73" s="2"/>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>64</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
         <v>65</v>
       </c>
-      <c r="B69">
+      <c r="B75">
         <f>1099+299</f>
         <v>1398</v>
       </c>
-      <c r="C69" s="2" t="s">
+      <c r="C75" s="2" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
         <v>68</v>
       </c>
-      <c r="B72" s="2" t="s">
+      <c r="B78" s="2" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
         <v>108</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B79" t="s">
         <v>109</v>
       </c>
     </row>

--- a/data/gravel/Sour Pasta Party 2025.xlsx
+++ b/data/gravel/Sour Pasta Party 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{806B0329-4062-9B40-99B9-48B9FC7F26C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDC45890-C2FE-EE4C-AE0A-2763F5E20CA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10000" yWindow="860" windowWidth="18800" windowHeight="16760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12780" yWindow="740" windowWidth="23720" windowHeight="16940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="119">
   <si>
     <t>brand</t>
   </si>
@@ -338,9 +338,6 @@
     <t>max_seat_insertion</t>
   </si>
   <si>
-    <t>a8:f32</t>
-  </si>
-  <si>
     <t>threaded 68</t>
   </si>
   <si>
@@ -350,9 +347,6 @@
     <t>EUR</t>
   </si>
   <si>
-    <t>rigid</t>
-  </si>
-  <si>
     <t>1099 frame</t>
   </si>
   <si>
@@ -381,6 +375,21 @@
   </si>
   <si>
     <t>fork_material</t>
+  </si>
+  <si>
+    <t>fork_travel</t>
+  </si>
+  <si>
+    <t>fork_sag</t>
+  </si>
+  <si>
+    <t>based on a 120 mm suspension fork</t>
+  </si>
+  <si>
+    <t>a8:f34</t>
+  </si>
+  <si>
+    <t>suspension</t>
   </si>
 </sst>
 </file>
@@ -720,7 +729,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F79"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -768,7 +777,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -776,7 +785,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -959,7 +968,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>12</v>
       </c>
@@ -979,7 +988,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>13</v>
       </c>
@@ -999,7 +1008,7 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -1019,7 +1028,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -1039,7 +1048,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>99</v>
       </c>
@@ -1059,7 +1068,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>100</v>
       </c>
@@ -1079,444 +1088,472 @@
         <v>315</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C23">
+        <v>120</v>
+      </c>
+      <c r="D23">
+        <v>120</v>
+      </c>
+      <c r="E23">
+        <v>120</v>
+      </c>
+      <c r="F23">
+        <v>120</v>
+      </c>
+      <c r="G23" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
         <v>23</v>
       </c>
-      <c r="D24">
+      <c r="D26">
         <v>2425</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
         <v>24</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B30" t="s">
         <v>24</v>
       </c>
-      <c r="C28">
+      <c r="C30">
         <v>700</v>
       </c>
-      <c r="D28">
+      <c r="D30">
         <v>700</v>
       </c>
-      <c r="E28">
+      <c r="E30">
         <v>700</v>
       </c>
-      <c r="F28">
+      <c r="F30">
         <v>700</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
         <v>25</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B31" t="s">
         <v>25</v>
       </c>
-      <c r="C29">
+      <c r="C31">
         <v>2.4</v>
       </c>
-      <c r="D29">
+      <c r="D31">
         <v>2.4</v>
       </c>
-      <c r="E29">
+      <c r="E31">
         <v>2.4</v>
       </c>
-      <c r="F29">
+      <c r="F31">
         <v>2.4</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
         <v>26</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B32" t="s">
         <v>26</v>
       </c>
-      <c r="C30">
+      <c r="C32">
         <v>2.4</v>
       </c>
-      <c r="D30">
+      <c r="D32">
         <v>2.4</v>
       </c>
-      <c r="E30">
+      <c r="E32">
         <v>2.4</v>
       </c>
-      <c r="F30">
+      <c r="F32">
         <v>2.4</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
         <v>27</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B33" t="s">
         <v>28</v>
       </c>
-      <c r="C31">
+      <c r="C33">
         <v>162</v>
       </c>
-      <c r="D31">
+      <c r="D33">
         <v>175</v>
       </c>
-      <c r="E31">
+      <c r="E33">
         <v>180</v>
       </c>
-      <c r="F31">
+      <c r="F33">
         <v>185</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
         <v>29</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B34" t="s">
         <v>30</v>
       </c>
-      <c r="C32">
+      <c r="C34">
         <v>170</v>
       </c>
-      <c r="D32">
+      <c r="D34">
         <v>183</v>
       </c>
-      <c r="E32">
+      <c r="E34">
         <v>188</v>
       </c>
-      <c r="F32">
+      <c r="F34">
         <v>196</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
         <v>31</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B36" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
         <v>69</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B37" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
         <v>70</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B38" s="2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
         <v>71</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
+      <c r="B39" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
         <v>33</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="B40" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
         <v>35</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B41" s="2" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
         <v>37</v>
       </c>
-      <c r="B41">
+      <c r="B43">
         <v>2.4</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
         <v>39</v>
       </c>
-      <c r="B43">
+      <c r="B45">
         <v>120</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
+      <c r="B46">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
         <v>42</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>43</v>
-      </c>
-      <c r="B47" s="2">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>44</v>
-      </c>
-      <c r="B48">
-        <v>110</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>110</v>
+        <v>43</v>
+      </c>
+      <c r="B49" s="2">
+        <v>148</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>111</v>
+        <v>44</v>
+      </c>
+      <c r="B50">
+        <v>110</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>45</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>46</v>
+        <v>113</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>47</v>
-      </c>
-      <c r="B57">
-        <v>31.6</v>
+        <v>45</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>48</v>
-      </c>
-      <c r="B58" s="2"/>
+        <v>46</v>
+      </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B59">
-        <v>38</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>50</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="B60" s="2"/>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>51</v>
+        <v>49</v>
+      </c>
+      <c r="B61">
+        <v>38</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>52</v>
-      </c>
-      <c r="B62">
-        <v>160</v>
+        <v>50</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>54</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>75</v>
+        <v>52</v>
+      </c>
+      <c r="B64">
+        <v>160</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>55</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>76</v>
+        <v>53</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>57</v>
+        <v>55</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>58</v>
-      </c>
-      <c r="B68">
-        <v>2</v>
+        <v>56</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>59</v>
-      </c>
-      <c r="B69">
-        <v>1</v>
+        <v>57</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>60</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>103</v>
+        <v>58</v>
+      </c>
+      <c r="B70">
+        <v>2</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B71">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>62</v>
-      </c>
-      <c r="B72" s="2"/>
+        <v>60</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>63</v>
-      </c>
-      <c r="B73" s="2"/>
+        <v>61</v>
+      </c>
+      <c r="B73">
+        <v>3</v>
+      </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>64</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>103</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="B74" s="2"/>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
+        <v>63</v>
+      </c>
+      <c r="B75" s="2"/>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>64</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
         <v>65</v>
       </c>
-      <c r="B75">
+      <c r="B77">
         <f>1099+299</f>
         <v>1398</v>
       </c>
-      <c r="C75" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
-        <v>67</v>
+      <c r="C77" s="2" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>68</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>104</v>
+        <v>66</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>108</v>
-      </c>
-      <c r="B79" t="s">
-        <v>109</v>
+        <v>67</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>68</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>106</v>
+      </c>
+      <c r="B81" t="s">
+        <v>107</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Sour Pasta Party 2025.xlsx
+++ b/data/gravel/Sour Pasta Party 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDC45890-C2FE-EE4C-AE0A-2763F5E20CA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8433864-FF52-3D4F-B130-B61225DCD753}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12780" yWindow="740" windowWidth="23720" windowHeight="16940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5080" yWindow="620" windowWidth="23720" windowHeight="16940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="122">
   <si>
     <t>brand</t>
   </si>
@@ -390,13 +390,22 @@
   </si>
   <si>
     <t>suspension</t>
+  </si>
+  <si>
+    <t>d</t>
+  </si>
+  <si>
+    <t>EC44</t>
+  </si>
+  <si>
+    <t>ZS44</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
       <color rgb="FF000000"/>
@@ -407,6 +416,11 @@
       <color rgb="FF000000"/>
       <name val="Futura"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Futura Medium"/>
     </font>
   </fonts>
   <fills count="2">
@@ -429,10 +443,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1027,6 +1042,9 @@
       <c r="F19">
         <v>520</v>
       </c>
+      <c r="G19" s="2" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
@@ -1123,7 +1141,8 @@
         <v>23</v>
       </c>
       <c r="D26">
-        <v>2425</v>
+        <f>2225</f>
+        <v>2225</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
@@ -1272,6 +1291,9 @@
       <c r="B39" s="2" t="s">
         <v>118</v>
       </c>
+      <c r="D39" s="2" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
@@ -1358,10 +1380,16 @@
       <c r="A52" t="s">
         <v>109</v>
       </c>
+      <c r="B52" s="3" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>110</v>
+      </c>
+      <c r="B53" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
